--- a/estandar-b/templates/3-2-plan-experimentacion.xlsx
+++ b/estandar-b/templates/3-2-plan-experimentacion.xlsx
@@ -13,7 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja de hipótesis · mínimo 3 po" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diseño de pruebas priorizadas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tabla 1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Referencia de trabajo del F21'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tu turno · preguntas guía'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Hoja de hipótesis · mínimo 3 po'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Diseño de pruebas priorizadas'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -30,17 +36,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <color rgb="004B5563"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,8 +59,13 @@
         <fgColor rgb="0028467E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,16 +73,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3E4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3E4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3E4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3E4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -446,7 +475,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mi CompañIA</t>
@@ -483,7 +512,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MiPyME</t>
@@ -530,7 +559,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -561,17 +590,17 @@
       <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Diseño de pruebas priorizadas Por cada prueba: hipótesis que valida, métricas de éxito, criterio de éxito (umbral), nivel de criticidad (alta/media/baja), nivel de confianza necesario, costo estimado, tiempo estimado, nombre de la prueba, responsable.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -587,17 +616,17 @@
       <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Plan de ejecución Cronograma de las pruebas: qué se ejecuta cuándo, quién es el responsable, cuánto tiempo toma cada sesión.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -620,7 +649,7 @@
     <col width="29" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -655,15 +684,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Ad1</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -677,15 +706,15 @@
       <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Ad3</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -695,15 +724,15 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>De1</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -717,15 +746,15 @@
       <c r="E8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>De3</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -735,15 +764,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Fa1</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -757,15 +786,15 @@
       <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Fa3</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -775,15 +804,15 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Vi1</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -797,15 +826,15 @@
       <c r="E16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Vi3</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -832,7 +861,7 @@
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -895,19 +924,19 @@
       <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -925,19 +954,19 @@
       <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">

--- a/estandar-b/templates/3-2-plan-experimentacion.xlsx
+++ b/estandar-b/templates/3-2-plan-experimentacion.xlsx
@@ -7,15 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referencia de trabajo del F21" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos del documento" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tu turno · preguntas guía" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja de hipótesis · mínimo 3 po" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diseño de pruebas priorizadas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tabla 1'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Referencia de trabajo del F21'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Datos del documento'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tu turno · preguntas guía'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Hoja de hipótesis · mínimo 3 po'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Diseño de pruebas priorizadas'!$1:$1</definedName>
@@ -27,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +38,24 @@
       <name val="Calibri"/>
       <color rgb="004B5563"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00529ED7"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0028467E"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0028467E"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -91,9 +108,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -467,28 +496,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mi CompañIA</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Plan de experimentación documentado Manual de Desarrollar con IA · Producto del Elemento 3 · Desarrollar · Excel</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Producto 3.2 Hoja editable · Excel Mi CompañIA · FUNDES</t>
+          <t>PLANTILLA DE TRABAJO · ESTÁNDAR B</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Plan de experimentación documentado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sobre este template. Hoja de cálculo con las hipótesis por categoría (adaptabilidad, deseabilidad, factibilidad, viabilidad), el diseño de las pruebas priorizadas y el cronograma de ejecución. Excel es el formato natural para esta clase de producto: te permite añadir filas conforme detectes más elementos, ordenar por puntaje y generar gráficas. Llénalo con datos de TU MiPyME real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de trabajo del F21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>•  (a) Contiene al menos tres hipótesis seleccionadas por el cliente de cada una de las siguientes categorías: adaptabilidad, deseabilidad, factibilidad y viabilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>•  (b) Contiene el diseño de las pruebas priorizadas: hipótesis, métricas, criterios de éxito, nivel de criticidad, nivel de confianza, costo, tiempo, nombre de la prueba, nombre del responsable y tiempo de duración</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>•  (c) Incluye la descripción del perfil de los usuarios participantes en las pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>•  (d) Contiene el plan de ejecución de las pruebas considerando la actividad, responsable y temporalidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>•  (e) Se presenta en formato digital/físico, con redacción clara y sin errores ortográficos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Caso pedagógico Artesanías Tonalli (ilustrativo): 12 hipótesis en total (3 por categoría). Ejemplos: Deseabilidad — "Los clientes de Tonalli preferirán comprar en línea si la descripción de cada pieza transmite su unicidad artesanal". Factibilidad — "Lucía puede operar el asistente de manera autónoma con una sola sesión de capacitación". Pruebas: 5 priorizadas, 10 usuarios participantes (4 clientes regulares, 3 clientes nuevos, 3 compradores potenciales vía Instagram).</t>
         </is>
       </c>
     </row>
@@ -513,32 +593,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>MiPyME</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr"/>
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr"/>
+      <c r="D1" s="5" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Consultor</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Responsable MiPyME</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -560,73 +640,73 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Pregunta guía</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Tu respuesta (llena con datos de TU MiPyME)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Hipótesis por categoría (mínimo 3 por cada una) Define al menos 3 hipótesis por categoría: adaptabilidad (¿la solución se adapta al contexto de la MiPyME?), deseabilidad (¿los usuarios la quieren?), factibilidad (¿es posible construirla y operarla?), viabilidad (¿genera valor económico?).</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Diseño de pruebas priorizadas Por cada prueba: hipótesis que valida, métricas de éxito, criterio de éxito (umbral), nivel de criticidad (alta/media/baja), nivel de confianza necesario, costo estimado, tiempo estimado, nombre de la prueba, responsable.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Perfil de usuarios participantes ¿Quiénes participarán en las pruebas? Describe el perfil de cada tipo de usuario: características, nivel de experiencia digital, relación con la MiPyME.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Plan de ejecución Cronograma de las pruebas: qué se ejecuta cuándo, quién es el responsable, cuánto tiempo toma cada sesión.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -650,191 +730,191 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Hipótesis</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Métrica de validación</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Criterio de éxito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Seleccionada por el cliente</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Categoría: Adaptabilidad</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Ad1</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Ad2</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Ad3</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Categoría: Deseabilidad</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>De1</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>De2</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>De3</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Categoría: Factibilidad</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Fa1</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Fa2</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr"/>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Fa3</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Categoría: Viabilidad</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Vi1</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr"/>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Vi2</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr"/>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Vi3</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -862,126 +942,126 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Nombre de la prueba</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Hipótesis que valida</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Métricas y criterio de éxito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Criticidad</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Confianza</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Costo est.</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Duración</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
